--- a/artfynd/A 39260-2022 artfynd.xlsx
+++ b/artfynd/A 39260-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445917</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135445920</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
